--- a/materials/ASMR_reporting_checklist.xlsx
+++ b/materials/ASMR_reporting_checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDBC1236-36AD-4A1B-BD1B-F59623484BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF71272F-A137-4C16-9E83-67E49FEBA804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{21B3515E-287D-4A43-88FD-660DD2486EA6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21B3515E-287D-4A43-88FD-660DD2486EA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="156">
   <si>
     <t>SECTION</t>
   </si>
@@ -92,9 +92,6 @@
     <t>Taxonomic and organismal scope (if any)</t>
   </si>
   <si>
-    <t>Materials and Methods</t>
-  </si>
-  <si>
     <t>Contextual information: time</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
   </si>
   <si>
     <t>eco:eventDurationUnit</t>
-  </si>
-  <si>
-    <t>(FIELD)</t>
   </si>
   <si>
     <t>eco:eventDurationValue</t>
@@ -585,6 +579,9 @@
   </si>
   <si>
     <t>e.g. pictures/video/samples</t>
+  </si>
+  <si>
+    <t>Materials and Methods (FIELD)</t>
   </si>
 </sst>
 </file>
@@ -736,7 +733,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -753,26 +750,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -794,6 +773,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1133,8 +1133,11 @@
   <dimension ref="A1:H87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
     <col min="2" max="2" width="22.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.21875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" customWidth="1"/>
     <col min="6" max="6" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1179,55 +1182,55 @@
       <c r="F2" s="4"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6" t="s">
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="8" t="b">
+      <c r="F3" s="15"/>
+      <c r="G3" s="14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="7" t="s">
+    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="7" t="s">
+      <c r="F4" s="17"/>
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="1:8" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="16"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:8" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -1240,325 +1243,323 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="F8" s="15"/>
+      <c r="G8" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="20"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:8" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="F11" s="15"/>
+      <c r="G11" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="6" t="s">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:8" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A14" s="15"/>
+      <c r="B14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="1:8" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="14" t="s">
+      <c r="E14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="F14" s="15"/>
+      <c r="G14" s="14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="14" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="8" t="b">
+      <c r="F15" s="17"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="17"/>
+      <c r="E16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="17"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="17"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="17"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="17"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="17"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="17"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="17"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="16"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="8"/>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="8"/>
-    </row>
-    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="8"/>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="8"/>
-    </row>
-    <row r="21" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="8"/>
-    </row>
-    <row r="22" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="10"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="6" t="s">
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7" t="s">
+      <c r="F24" s="17"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="8" t="b">
+      <c r="F25" s="17"/>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="17"/>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="17"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="17"/>
+      <c r="G28" s="14"/>
+    </row>
+    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="16"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="1:7" ht="374.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="15"/>
+      <c r="E30" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="14" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:7" ht="360" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="14" t="s">
+    <row r="31" spans="1:7" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="14" t="s">
+      <c r="D31" s="16"/>
+      <c r="E31" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="8"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="14"/>
     </row>
     <row r="32" spans="1:7" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1567,355 +1568,355 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6" t="s">
+    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="15"/>
+      <c r="E33" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" s="6"/>
+      <c r="F33" s="15"/>
       <c r="G33" s="5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="F34" s="10"/>
+    <row r="34" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="16"/>
       <c r="G34" s="5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="231" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F35" s="4"/>
-      <c r="G35" s="18" t="s">
-        <v>67</v>
+      <c r="G35" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="15"/>
+      <c r="B37" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="15"/>
+      <c r="E37" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="F37" s="15"/>
+      <c r="G37" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="7" t="s">
+    </row>
+    <row r="38" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="16"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="5" t="s">
+      <c r="F38" s="16"/>
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="15"/>
+      <c r="B39" s="15" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="13" t="s">
+      <c r="C39" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="5"/>
-    </row>
-    <row r="39" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6" t="s">
+      <c r="D39" s="15"/>
+      <c r="E39" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="F39" s="15"/>
+      <c r="G39" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="7" t="s">
+    </row>
+    <row r="40" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="5" t="s">
+      <c r="D40" s="17"/>
+      <c r="E40" s="6" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="144" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="14" t="s">
+      <c r="F40" s="17"/>
+      <c r="G40" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D40" s="9"/>
-      <c r="E40" s="7" t="s">
+      <c r="D41" s="17"/>
+      <c r="E41" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="14" t="s">
+      <c r="F41" s="17"/>
+      <c r="G41" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="16"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" s="16"/>
+      <c r="G42" s="5"/>
+    </row>
+    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="15"/>
+      <c r="B43" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="D41" s="9"/>
-      <c r="E41" s="7" t="s">
+      <c r="C43" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F42" s="10"/>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6" t="s">
+      <c r="D43" s="15"/>
+      <c r="E43" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="F43" s="15"/>
+      <c r="G43" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D43" s="6"/>
-      <c r="E43" s="7" t="s">
+      <c r="F44" s="17"/>
+      <c r="G44" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
+      <c r="D45" s="17"/>
+      <c r="E45" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="7" t="s">
+      <c r="F45" s="17"/>
+      <c r="G45" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="16"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="10"/>
+      <c r="F46" s="16"/>
       <c r="G46" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6" t="s">
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="15"/>
+      <c r="B50" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="202.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="4" t="s">
+      <c r="C50" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6" t="s">
+      <c r="D50" s="15"/>
+      <c r="E50" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="F50" s="15"/>
+      <c r="G50" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="5"/>
+    </row>
+    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="15"/>
+      <c r="B52" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6" t="s">
+      <c r="C52" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="5"/>
-    </row>
-    <row r="52" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6" t="s">
+      <c r="D52" s="15"/>
+      <c r="E52" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="F52" s="15"/>
+      <c r="G52" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="14" t="s">
+      <c r="F53" s="17"/>
+      <c r="G53" s="14"/>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="16"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="14"/>
+    </row>
+    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="15"/>
+      <c r="B55" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A53" s="9"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="14" t="s">
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="8"/>
-    </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="10"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="8"/>
-    </row>
-    <row r="55" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6" t="s">
+      <c r="F55" s="15"/>
+      <c r="G55" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="16"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F56" s="10"/>
+      <c r="F56" s="16"/>
       <c r="G56" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -1925,10 +1926,10 @@
     <row r="58" spans="1:7" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -1937,455 +1938,461 @@
     </row>
     <row r="59" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="303" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6" t="s">
+      <c r="A61" s="15"/>
+      <c r="B61" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="F61" s="15"/>
+      <c r="G61" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="16"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="5"/>
+    </row>
+    <row r="63" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A63" s="15"/>
+      <c r="B63" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6" t="s">
+      <c r="C63" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="6"/>
-      <c r="G61" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6" t="s">
+      <c r="D63" s="15"/>
+      <c r="E63" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="F63" s="15"/>
+      <c r="G63" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="14" t="s">
+      <c r="D64" s="17"/>
+      <c r="E64" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="9"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="14" t="s">
+      <c r="F64" s="17"/>
+      <c r="G64" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D64" s="9"/>
-      <c r="E64" s="14" t="s">
+      <c r="F65" s="17"/>
+      <c r="G65" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F64" s="9"/>
-      <c r="G64" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="14" t="s">
+      <c r="F66" s="17"/>
+      <c r="G66" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="16"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F65" s="9"/>
-      <c r="G65" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="9"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="14" t="s">
+      <c r="F67" s="16"/>
+      <c r="G67" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F66" s="9"/>
-      <c r="G66" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="10"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="4" t="s">
+      <c r="B68" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="F67" s="10"/>
-      <c r="G67" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="403.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="288" x14ac:dyDescent="0.3">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A72" s="15"/>
+      <c r="B72" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" s="15"/>
+      <c r="E72" s="15"/>
+      <c r="F72" s="15"/>
       <c r="G72" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="10"/>
-      <c r="B73" s="10"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="288.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="16"/>
+      <c r="B73" s="16"/>
       <c r="C73" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
+        <v>134</v>
+      </c>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
       <c r="G73" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6" t="s">
+      <c r="A75" s="15"/>
+      <c r="B75" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="16"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C75" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="10"/>
-      <c r="B76" s="10"/>
-      <c r="C76" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
+      <c r="D76" s="16"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
       <c r="G76" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="346.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="360.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>142</v>
+        <v>139</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="360.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="389.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6" t="s">
+      <c r="A80" s="15"/>
+      <c r="B80" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="17"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="9"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="14"/>
+    </row>
+    <row r="82" spans="1:7" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="16"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="D82" s="16"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="14"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="15"/>
+      <c r="B83" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="D80" s="6"/>
-      <c r="E80" s="6"/>
-      <c r="F80" s="6"/>
-      <c r="G80" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="8"/>
-    </row>
-    <row r="82" spans="1:7" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="10"/>
-      <c r="B82" s="10"/>
-      <c r="C82" s="4" t="s">
+      <c r="C83" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="8"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6" t="s">
+      <c r="D83" s="15"/>
+      <c r="E83" s="15"/>
+      <c r="F83" s="15"/>
+      <c r="G83" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="16"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="16"/>
+      <c r="D84" s="16"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="16"/>
+      <c r="G84" s="14"/>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="15"/>
+      <c r="B85" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C85" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="D83" s="6"/>
-      <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
-      <c r="G83" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="10"/>
-      <c r="B84" s="10"/>
-      <c r="C84" s="10"/>
-      <c r="D84" s="10"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="8"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D85" s="6"/>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="8" t="s">
-        <v>92</v>
+      <c r="D85" s="15"/>
+      <c r="E85" s="15"/>
+      <c r="F85" s="15"/>
+      <c r="G85" s="14" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="10"/>
-      <c r="B86" s="10"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="10"/>
-      <c r="E86" s="10"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="8"/>
-    </row>
-    <row r="87" spans="1:7" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="16"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16"/>
+      <c r="G86" s="14"/>
+    </row>
+    <row r="87" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="F83:F84"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="B80:B82"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="F80:F82"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="B63:B67"/>
-    <mergeCell ref="D63:D67"/>
-    <mergeCell ref="F63:F67"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="F55:F56"/>
+  <mergeCells count="114">
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G23:G29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="D14:D22"/>
+    <mergeCell ref="F14:F22"/>
+    <mergeCell ref="G14:G22"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="B23:B29"/>
+    <mergeCell ref="C23:C29"/>
+    <mergeCell ref="D23:D29"/>
+    <mergeCell ref="F23:F29"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="F43:F46"/>
     <mergeCell ref="F50:F51"/>
     <mergeCell ref="A52:A54"/>
     <mergeCell ref="B52:B54"/>
@@ -2402,57 +2409,52 @@
     <mergeCell ref="C50:C51"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="E50:E51"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="G23:G29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="D14:D22"/>
-    <mergeCell ref="F14:F22"/>
-    <mergeCell ref="G14:G22"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="B23:B29"/>
-    <mergeCell ref="C23:C29"/>
-    <mergeCell ref="D23:D29"/>
-    <mergeCell ref="F23:F29"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="B63:B67"/>
+    <mergeCell ref="D63:D67"/>
+    <mergeCell ref="F63:F67"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="F80:F82"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="G83:G84"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" location="eco_geospatialScopeAreaUnit" display="https://eco.tdwg.org/list/ - eco_geospatialScopeAreaUnit" xr:uid="{233C4592-B363-429A-A8DA-9920773BA85D}"/>

--- a/materials/ASMR_reporting_checklist.xlsx
+++ b/materials/ASMR_reporting_checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF71272F-A137-4C16-9E83-67E49FEBA804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7503A314-8FBA-4C5D-A923-8F319CDDFB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21B3515E-287D-4A43-88FD-660DD2486EA6}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{21B3515E-287D-4A43-88FD-660DD2486EA6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,9 +59,6 @@
     <t>REPORTED</t>
   </si>
   <si>
-    <t>BO_ET_AL_2011</t>
-  </si>
-  <si>
     <t>JACOBSEN ET AL., 2024</t>
   </si>
   <si>
@@ -582,6 +579,9 @@
   </si>
   <si>
     <t>Materials and Methods (FIELD)</t>
+  </si>
+  <si>
+    <t>Bo et al., 2011</t>
   </si>
 </sst>
 </file>
@@ -733,7 +733,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
@@ -774,26 +774,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1133,15 +1134,17 @@
   <dimension ref="A1:H87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" customWidth="1"/>
+    <col min="1" max="1" width="29.77734375" customWidth="1"/>
+    <col min="2" max="2" width="57.5546875" customWidth="1"/>
     <col min="3" max="3" width="48.33203125" customWidth="1"/>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
     <col min="5" max="5" width="33.44140625" customWidth="1"/>
     <col min="6" max="6" width="20.44140625" customWidth="1"/>
+    <col min="7" max="7" width="18.88671875" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,79 +1164,79 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15" t="s">
+    <row r="3" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="15"/>
+      <c r="G4" s="17"/>
+    </row>
+    <row r="5" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="15"/>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F6" s="16"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:8" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G6" s="17"/>
+    </row>
+    <row r="7" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -1243,323 +1246,323 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B8" s="15" t="s">
+    <row r="8" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="14"/>
+      <c r="G8" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="21"/>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="D11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="14"/>
+      <c r="G11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="14" t="s">
+    </row>
+    <row r="12" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F12" s="15"/>
+      <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16"/>
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
       <c r="E13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+    </row>
+    <row r="14" spans="1:8" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:8" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A14" s="15"/>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="14"/>
+      <c r="G14" s="17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15"/>
+      <c r="B15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="17"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="17"/>
+    </row>
+    <row r="16" spans="1:8" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="15"/>
       <c r="B16" s="10"/>
       <c r="C16" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="17"/>
+    </row>
+    <row r="17" spans="1:7" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="15"/>
       <c r="B17" s="10"/>
       <c r="C17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="17"/>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="17"/>
+    </row>
+    <row r="18" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="15"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
-      <c r="D18" s="17"/>
+      <c r="D18" s="15"/>
       <c r="E18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
+        <v>36</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="17"/>
+    </row>
+    <row r="19" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
-      <c r="D19" s="17"/>
+      <c r="D19" s="15"/>
       <c r="E19" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
+        <v>37</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
+    </row>
+    <row r="20" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
-      <c r="D20" s="17"/>
+      <c r="D20" s="15"/>
       <c r="E20" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14"/>
-    </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
+        <v>38</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="17"/>
+    </row>
+    <row r="21" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15"/>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
-      <c r="D21" s="17"/>
+      <c r="D21" s="15"/>
       <c r="E21" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14"/>
-    </row>
-    <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="17"/>
+    </row>
+    <row r="22" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="16"/>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="16"/>
       <c r="E22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+    </row>
+    <row r="23" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="D23" s="14"/>
+      <c r="E23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="6" t="s">
+      <c r="F23" s="14"/>
+      <c r="G23" s="17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="15"/>
+      <c r="G24" s="17"/>
+    </row>
+    <row r="25" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="14"/>
-    </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="15"/>
+      <c r="G25" s="17"/>
+    </row>
+    <row r="26" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="14"/>
-    </row>
-    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="8" t="s">
+      <c r="F26" s="15"/>
+      <c r="G26" s="17"/>
+    </row>
+    <row r="27" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="14"/>
-    </row>
-    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="8" t="s">
+      <c r="F27" s="15"/>
+      <c r="G27" s="17"/>
+    </row>
+    <row r="28" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="14"/>
-    </row>
-    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F28" s="15"/>
+      <c r="G28" s="17"/>
+    </row>
+    <row r="29" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
       <c r="E29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
+    </row>
+    <row r="30" spans="1:7" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="14"/>
+      <c r="B30" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="14"/>
-    </row>
-    <row r="30" spans="1:7" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="15"/>
-      <c r="B30" s="15" t="s">
+      <c r="C30" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="14"/>
+      <c r="E30" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="14" t="b">
+      <c r="F30" s="14"/>
+      <c r="G30" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" s="18" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16"/>
       <c r="B31" s="16"/>
       <c r="C31" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F31" s="16"/>
-      <c r="G31" s="14"/>
-    </row>
-    <row r="32" spans="1:7" ht="173.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G31" s="17"/>
+    </row>
+    <row r="32" spans="1:7" s="18" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -1568,273 +1571,273 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15" t="s">
+    <row r="33" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="14"/>
+      <c r="B33" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="D33" s="14"/>
+      <c r="E33" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F33" s="15"/>
+      <c r="F33" s="14"/>
       <c r="G33" s="5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
       <c r="E34" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" s="18" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F35" s="4"/>
       <c r="G35" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="18" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F36" s="4"/>
       <c r="G36" s="5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15" t="s">
+    <row r="37" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="D37" s="14"/>
+      <c r="E37" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D37" s="15"/>
-      <c r="E37" s="6" t="s">
+      <c r="F37" s="14"/>
+      <c r="G37" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F37" s="15"/>
-      <c r="G37" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="16"/>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F38" s="16"/>
       <c r="G38" s="5"/>
     </row>
-    <row r="39" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15" t="s">
+    <row r="39" spans="1:7" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="D39" s="14"/>
+      <c r="E39" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D39" s="15"/>
-      <c r="E39" s="6" t="s">
+      <c r="F39" s="14"/>
+      <c r="G39" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="5" t="s">
+    </row>
+    <row r="40" spans="1:7" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="144" x14ac:dyDescent="0.3">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="8" t="s">
+      <c r="D40" s="15"/>
+      <c r="E40" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="17"/>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="15"/>
+      <c r="G40" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="15"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F40" s="17"/>
-      <c r="G40" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="8" t="s">
+      <c r="D41" s="15"/>
+      <c r="E41" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F41" s="17"/>
+      <c r="F41" s="15"/>
       <c r="G41" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="16"/>
       <c r="B42" s="16"/>
       <c r="C42" s="11"/>
       <c r="D42" s="16"/>
       <c r="E42" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42" s="16"/>
       <c r="G42" s="5"/>
     </row>
-    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15" t="s">
+    <row r="43" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="D43" s="14"/>
+      <c r="E43" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D43" s="15"/>
-      <c r="E43" s="6" t="s">
+      <c r="F43" s="14"/>
+      <c r="G43" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="15"/>
+      <c r="B44" s="15"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F43" s="15"/>
-      <c r="G43" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="6" t="s">
+      <c r="F44" s="15"/>
+      <c r="G44" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F44" s="17"/>
-      <c r="G44" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" s="17"/>
+      <c r="F45" s="15"/>
       <c r="G45" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="16"/>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
       <c r="E46" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F46" s="16"/>
       <c r="G46" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="18" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="14"/>
+      <c r="B48" s="14" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15" t="s">
+      <c r="C48" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
       <c r="G48" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="18" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="16"/>
       <c r="B49" s="16"/>
       <c r="C49" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D49" s="16"/>
       <c r="E49" s="16"/>
       <c r="F49" s="16"/>
       <c r="G49" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="14"/>
+      <c r="B50" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="D50" s="14"/>
+      <c r="E50" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="F50" s="15"/>
+      <c r="F50" s="14"/>
       <c r="G50" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -1843,149 +1846,149 @@
       <c r="F51" s="16"/>
       <c r="G51" s="5"/>
     </row>
-    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="15"/>
-      <c r="B52" s="15" t="s">
+    <row r="52" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="14"/>
+      <c r="B52" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="D52" s="14"/>
+      <c r="E52" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D52" s="15"/>
-      <c r="E52" s="8" t="s">
+      <c r="F52" s="14"/>
+      <c r="G52" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F52" s="15"/>
-      <c r="G52" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F53" s="17"/>
-      <c r="G53" s="14"/>
-    </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F53" s="15"/>
+      <c r="G53" s="17"/>
+    </row>
+    <row r="54" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="16"/>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
       <c r="E54" s="4"/>
       <c r="F54" s="16"/>
-      <c r="G54" s="14"/>
-    </row>
-    <row r="55" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15" t="s">
+      <c r="G54" s="17"/>
+    </row>
+    <row r="55" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="14"/>
+      <c r="B55" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="F55" s="15"/>
+      <c r="F55" s="14"/>
       <c r="G55" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="16"/>
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
       <c r="E56" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F56" s="16"/>
       <c r="G56" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="C57" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="5"/>
     </row>
-    <row r="58" spans="1:7" ht="216.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" s="18" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="5"/>
     </row>
-    <row r="59" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" s="18" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="C59" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="303" thickBot="1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" s="18" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="15"/>
-      <c r="B61" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="14"/>
+      <c r="B61" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="D61" s="14"/>
+      <c r="E61" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D61" s="15"/>
-      <c r="E61" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="F61" s="15"/>
+      <c r="F61" s="14"/>
       <c r="G61" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="16"/>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -1994,365 +1997,434 @@
       <c r="F62" s="16"/>
       <c r="G62" s="5"/>
     </row>
-    <row r="63" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="15"/>
-      <c r="B63" s="15" t="s">
+    <row r="63" spans="1:7" s="18" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="14"/>
+      <c r="B63" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="D63" s="14"/>
+      <c r="E63" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D63" s="15"/>
-      <c r="E63" s="8" t="s">
+      <c r="F63" s="14"/>
+      <c r="G63" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A64" s="15"/>
+      <c r="B64" s="15"/>
+      <c r="C64" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="F63" s="15"/>
-      <c r="G63" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="8" t="s">
+      <c r="D64" s="15"/>
+      <c r="E64" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D64" s="17"/>
-      <c r="E64" s="8" t="s">
+      <c r="F64" s="15"/>
+      <c r="G64" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="15"/>
+      <c r="B65" s="15"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F64" s="17"/>
-      <c r="G64" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="8" t="s">
+      <c r="F65" s="15"/>
+      <c r="G65" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="15"/>
+      <c r="B66" s="15"/>
+      <c r="C66" s="10"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F65" s="17"/>
-      <c r="G65" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F66" s="17"/>
+      <c r="F66" s="15"/>
       <c r="G66" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="16"/>
       <c r="B67" s="16"/>
       <c r="C67" s="11"/>
       <c r="D67" s="16"/>
       <c r="E67" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F67" s="16"/>
       <c r="G67" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="245.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" s="18" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" s="18" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" s="18" customFormat="1" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A72" s="15"/>
-      <c r="B72" s="15" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="14"/>
+      <c r="B72" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
       <c r="G72" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="288.60000000000002" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" s="18" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="16"/>
       <c r="B73" s="16"/>
       <c r="C73" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D73" s="16"/>
       <c r="E73" s="16"/>
       <c r="F73" s="16"/>
       <c r="G73" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="15"/>
-      <c r="B75" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="14"/>
+      <c r="B75" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C75" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
       <c r="G75" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="274.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" s="18" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="16"/>
       <c r="B76" s="16"/>
       <c r="C76" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D76" s="16"/>
       <c r="E76" s="16"/>
       <c r="F76" s="16"/>
       <c r="G76" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="360.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" s="18" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C77" s="13" t="s">
         <v>139</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>140</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" s="18" customFormat="1" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="C78" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="389.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" s="18" customFormat="1" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="G79" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="15"/>
-      <c r="B80" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="14"/>
+      <c r="B80" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="17"/>
-      <c r="B81" s="17"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="15"/>
+      <c r="B81" s="15"/>
       <c r="C81" s="9"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="14"/>
-    </row>
-    <row r="82" spans="1:7" ht="130.19999999999999" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="17"/>
+    </row>
+    <row r="82" spans="1:7" s="18" customFormat="1" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="16"/>
       <c r="B82" s="16"/>
       <c r="C82" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D82" s="16"/>
       <c r="E82" s="16"/>
       <c r="F82" s="16"/>
-      <c r="G82" s="14"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="15"/>
-      <c r="B83" s="15" t="s">
+      <c r="G82" s="17"/>
+    </row>
+    <row r="83" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="14"/>
+      <c r="B83" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C83" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C83" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="D83" s="15"/>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
-      <c r="G83" s="14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D83" s="14"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="16"/>
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
       <c r="D84" s="16"/>
       <c r="E84" s="16"/>
       <c r="F84" s="16"/>
-      <c r="G84" s="14"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="15"/>
-      <c r="B85" s="15" t="s">
+      <c r="G84" s="17"/>
+    </row>
+    <row r="85" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="14"/>
+      <c r="B85" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C85" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="C85" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D85" s="15"/>
-      <c r="E85" s="15"/>
-      <c r="F85" s="15"/>
-      <c r="G85" s="14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="16"/>
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
       <c r="E86" s="16"/>
       <c r="F86" s="16"/>
-      <c r="G86" s="14"/>
-    </row>
-    <row r="87" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G86" s="17"/>
+    </row>
+    <row r="87" spans="1:7" s="18" customFormat="1" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="114">
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="G3:G6"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="E85:E86"/>
+    <mergeCell ref="F85:F86"/>
+    <mergeCell ref="G80:G82"/>
+    <mergeCell ref="A83:A84"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="D83:D84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="D75:D76"/>
+    <mergeCell ref="E75:E76"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="B80:B82"/>
+    <mergeCell ref="D80:D82"/>
+    <mergeCell ref="E80:E82"/>
+    <mergeCell ref="F80:F82"/>
+    <mergeCell ref="A63:A67"/>
+    <mergeCell ref="B63:B67"/>
+    <mergeCell ref="D63:D67"/>
+    <mergeCell ref="F63:F67"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="F61:F62"/>
+    <mergeCell ref="G52:G54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="F52:F54"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="F39:F42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="F37:F38"/>
     <mergeCell ref="A11:A13"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="C11:C13"/>
@@ -2374,87 +2446,18 @@
     <mergeCell ref="C23:C29"/>
     <mergeCell ref="D23:D29"/>
     <mergeCell ref="F23:F29"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="F39:F42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="F50:F51"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="E50:E51"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="F61:F62"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="A63:A67"/>
-    <mergeCell ref="B63:B67"/>
-    <mergeCell ref="D63:D67"/>
-    <mergeCell ref="F63:F67"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="D75:D76"/>
-    <mergeCell ref="E75:E76"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="B80:B82"/>
-    <mergeCell ref="D80:D82"/>
-    <mergeCell ref="E80:E82"/>
-    <mergeCell ref="F80:F82"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="A85:A86"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="E85:E86"/>
-    <mergeCell ref="F85:F86"/>
-    <mergeCell ref="G80:G82"/>
-    <mergeCell ref="A83:A84"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="D83:D84"/>
-    <mergeCell ref="E83:E84"/>
-    <mergeCell ref="F83:F84"/>
-    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="G8:G10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" location="eco_geospatialScopeAreaUnit" display="https://eco.tdwg.org/list/ - eco_geospatialScopeAreaUnit" xr:uid="{233C4592-B363-429A-A8DA-9920773BA85D}"/>
